--- a/hall/resources/sample/PassList.xlsx
+++ b/hall/resources/sample/PassList.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>ID</t>
   </si>
@@ -44,6 +49,12 @@
     <t>是否跟随赛季进行</t>
   </si>
   <si>
+    <t>初级付费金额</t>
+  </si>
+  <si>
+    <t>高级付费金额</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -60,6 +71,12 @@
   </si>
   <si>
     <t>FollowsSeason</t>
+  </si>
+  <si>
+    <t>ShopRechargeListID</t>
+  </si>
+  <si>
+    <t>ShopRechargeList1ID</t>
   </si>
   <si>
     <t>每日签到</t>
@@ -705,7 +722,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -717,6 +734,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1250,16 +1270,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="12.5" customWidth="1"/>
     <col min="3" max="3" width="10.25" customWidth="1"/>
     <col min="4" max="4" width="10.75" customWidth="1"/>
     <col min="5" max="5" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="19.375" customWidth="1"/>
+    <col min="7" max="7" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:6">
+    <row r="1" ht="16.5" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,49 +1297,63 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" ht="16.5" spans="1:6">
+    <row r="2" ht="16.5" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" ht="17.25" spans="1:6">
+    <row r="3" ht="17.25" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" ht="16.5" spans="1:6">
+    <row r="4" ht="16.5" spans="1:7">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
     </row>
-    <row r="5" ht="16.5" spans="1:6">
+    <row r="5" ht="16.5" spans="1:7">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
@@ -1325,7 +1361,7 @@
         <v>4061014</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="b">
         <v>0</v>
@@ -1333,9 +1369,14 @@
       <c r="E5" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" s="4">
+        <v>1004</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1011</v>
+      </c>
     </row>
-    <row r="6" ht="16.5" spans="1:6">
+    <row r="6" ht="16.5" spans="1:7">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
@@ -1343,7 +1384,7 @@
         <v>4061015</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D6" s="1" t="b">
         <v>1</v>
@@ -1351,9 +1392,14 @@
       <c r="E6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="4">
+        <v>1004</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1011</v>
+      </c>
     </row>
-    <row r="7" ht="16.5" spans="1:6">
+    <row r="7" ht="16.5" spans="1:7">
       <c r="A7" s="1">
         <v>1003</v>
       </c>
@@ -1361,7 +1407,7 @@
         <v>4061016</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1" t="b">
         <v>1</v>
@@ -1369,9 +1415,14 @@
       <c r="E7" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F7" s="1"/>
+      <c r="F7" s="4">
+        <v>1004</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1011</v>
+      </c>
     </row>
-    <row r="8" ht="16.5" spans="1:6">
+    <row r="8" ht="16.5" spans="1:7">
       <c r="A8" s="1">
         <v>1004</v>
       </c>
@@ -1379,7 +1430,7 @@
         <v>4061017</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D8" s="1" t="b">
         <v>1</v>
@@ -1387,9 +1438,14 @@
       <c r="E8" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="4">
+        <v>1004</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1011</v>
+      </c>
     </row>
-    <row r="9" ht="16.5" spans="1:6">
+    <row r="9" ht="16.5" spans="1:7">
       <c r="A9" s="1">
         <v>1005</v>
       </c>
@@ -1397,7 +1453,7 @@
         <v>4061018</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D9" s="1" t="b">
         <v>1</v>
@@ -1405,9 +1461,14 @@
       <c r="E9" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="4">
+        <v>1004</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1011</v>
+      </c>
     </row>
-    <row r="10" ht="16.5" spans="1:6">
+    <row r="10" ht="16.5" spans="1:7">
       <c r="A10" s="1">
         <v>1006</v>
       </c>
@@ -1415,7 +1476,7 @@
         <v>4061019</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1" t="b">
         <v>1</v>
@@ -1423,7 +1484,12 @@
       <c r="E10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="F10" s="1"/>
+      <c r="F10" s="4">
+        <v>1004</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1011</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B10">

--- a/hall/resources/sample/PassList.xlsx
+++ b/hall/resources/sample/PassList.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
@@ -46,9 +46,6 @@
     <t>是否开启</t>
   </si>
   <si>
-    <t>是否跟随赛季进行</t>
-  </si>
-  <si>
     <t>初级付费金额</t>
   </si>
   <si>
@@ -70,9 +67,6 @@
     <t>isOpen</t>
   </si>
   <si>
-    <t>FollowsSeason</t>
-  </si>
-  <si>
     <t>ShopRechargeListID</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
   </si>
   <si>
     <t>赛季币达人</t>
-  </si>
-  <si>
-    <t>用户等级</t>
   </si>
 </sst>
 </file>
@@ -1270,18 +1261,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="12.5" customWidth="1"/>
     <col min="3" max="3" width="10.25" customWidth="1"/>
     <col min="4" max="4" width="10.75" customWidth="1"/>
-    <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="19.375" customWidth="1"/>
-    <col min="7" max="7" width="19.625" customWidth="1"/>
+    <col min="5" max="5" width="19.375" customWidth="1"/>
+    <col min="6" max="6" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:7">
+    <row r="1" ht="16.5" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1300,60 +1290,50 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" ht="16.5" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="17.25" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" ht="17.25" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="4" ht="16.5" spans="1:7">
+    <row r="4" ht="16.5" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
     </row>
-    <row r="5" ht="16.5" spans="1:7">
+    <row r="5" ht="16.5" spans="1:6">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
@@ -1361,22 +1341,19 @@
         <v>4061014</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="b">
-        <v>1</v>
+      <c r="E5" s="4">
+        <v>1004</v>
       </c>
       <c r="F5" s="4">
-        <v>1004</v>
-      </c>
-      <c r="G5" s="4">
         <v>1011</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:7">
+    <row r="6" ht="16.5" spans="1:6">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
@@ -1384,22 +1361,19 @@
         <v>4061015</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="b">
-        <v>1</v>
+      <c r="E6" s="4">
+        <v>1004</v>
       </c>
       <c r="F6" s="4">
-        <v>1004</v>
-      </c>
-      <c r="G6" s="4">
         <v>1011</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:7">
+    <row r="7" ht="16.5" spans="1:6">
       <c r="A7" s="1">
         <v>1003</v>
       </c>
@@ -1407,22 +1381,19 @@
         <v>4061016</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="1" t="b">
-        <v>1</v>
+      <c r="E7" s="4">
+        <v>1004</v>
       </c>
       <c r="F7" s="4">
-        <v>1004</v>
-      </c>
-      <c r="G7" s="4">
         <v>1011</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:7">
+    <row r="8" ht="16.5" spans="1:6">
       <c r="A8" s="1">
         <v>1004</v>
       </c>
@@ -1430,22 +1401,19 @@
         <v>4061017</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="1" t="b">
-        <v>1</v>
+      <c r="E8" s="4">
+        <v>1004</v>
       </c>
       <c r="F8" s="4">
-        <v>1004</v>
-      </c>
-      <c r="G8" s="4">
         <v>1011</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:7">
+    <row r="9" ht="16.5" spans="1:6">
       <c r="A9" s="1">
         <v>1005</v>
       </c>
@@ -1453,43 +1421,25 @@
         <v>4061018</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="1" t="b">
-        <v>1</v>
+      <c r="E9" s="4">
+        <v>1004</v>
       </c>
       <c r="F9" s="4">
-        <v>1004</v>
-      </c>
-      <c r="G9" s="4">
         <v>1011</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:7">
-      <c r="A10" s="1">
-        <v>1006</v>
-      </c>
-      <c r="B10" s="3">
-        <v>4061019</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>1004</v>
-      </c>
-      <c r="G10" s="4">
-        <v>1011</v>
-      </c>
+    <row r="10" ht="16.5" spans="1:6">
+      <c r="A10" s="1"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B10">
